--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/NEBRASKA_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/NEBRASKA_2016.xlsx
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C122">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C201">
